--- a/training_iterations.xlsx
+++ b/training_iterations.xlsx
@@ -485,31 +485,31 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5100829629629631</v>
+        <v>0.5594132962962963</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3550037037037037</v>
+        <v>0.475137037037037</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6003851851851851</v>
+        <v>0.6501666666666667</v>
       </c>
       <c r="E2" t="n">
-        <v>60.05</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G2" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H2" t="n">
-        <v>53.67142315430683</v>
+        <v>82.66441930179445</v>
       </c>
       <c r="I2" t="n">
-        <v>-45.93876366149934</v>
+        <v>-2.768523764115463</v>
       </c>
       <c r="J2" t="n">
-        <v>133.847105776413</v>
+        <v>160.2456432542369</v>
       </c>
     </row>
     <row r="3">
@@ -517,31 +517,31 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5219033703703704</v>
+        <v>0.5724847407407406</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2663814814814815</v>
+        <v>0.471462962962963</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6166925925925926</v>
+        <v>0.6513037037037037</v>
       </c>
       <c r="E3" t="n">
-        <v>60.83</v>
+        <v>65.48</v>
       </c>
       <c r="F3" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H3" t="n">
-        <v>55.16996828285933</v>
+        <v>76.11317163740033</v>
       </c>
       <c r="I3" t="n">
-        <v>-82.78899429185044</v>
+        <v>-39.69023112293367</v>
       </c>
       <c r="J3" t="n">
-        <v>152.3724513703801</v>
+        <v>155.2583401829805</v>
       </c>
     </row>
     <row r="4">
@@ -549,31 +549,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5157055925925926</v>
+        <v>0.5710787037037037</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2705296296296296</v>
+        <v>0.4725888888888889</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6117444444444444</v>
+        <v>0.6512592592592592</v>
       </c>
       <c r="E4" t="n">
-        <v>61.51</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H4" t="n">
-        <v>54.60526904293949</v>
+        <v>89.21189218904505</v>
       </c>
       <c r="I4" t="n">
-        <v>-36.58872168992324</v>
+        <v>8.559124552956121</v>
       </c>
       <c r="J4" t="n">
-        <v>136.7607343439365</v>
+        <v>174.4415013229798</v>
       </c>
     </row>
     <row r="5">
@@ -581,31 +581,31 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5117086296296296</v>
+        <v>0.577160851851852</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2824740740740741</v>
+        <v>0.4699259259259259</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5860814814814815</v>
+        <v>0.6249444444444444</v>
       </c>
       <c r="E5" t="n">
-        <v>59.52</v>
+        <v>65.83</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="G5" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H5" t="n">
-        <v>60.96006743517315</v>
+        <v>80.79863153967594</v>
       </c>
       <c r="I5" t="n">
-        <v>-43.90186524010231</v>
+        <v>18.05211512830479</v>
       </c>
       <c r="J5" t="n">
-        <v>173.234672871867</v>
+        <v>159.0471593650489</v>
       </c>
     </row>
     <row r="6">
@@ -613,31 +613,31 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5093275555555556</v>
+        <v>0.5594226296296295</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3157962962962963</v>
+        <v>0.4520333333333333</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6157814814814815</v>
+        <v>0.6430777777777777</v>
       </c>
       <c r="E6" t="n">
-        <v>60.17</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H6" t="n">
-        <v>63.23833286591165</v>
+        <v>81.62725908404917</v>
       </c>
       <c r="I6" t="n">
-        <v>-17.53262866556206</v>
+        <v>-11.3159233337309</v>
       </c>
       <c r="J6" t="n">
-        <v>171.7743258519166</v>
+        <v>174.5246368995974</v>
       </c>
     </row>
     <row r="7">
@@ -645,31 +645,31 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.5199547777777778</v>
+        <v>0.567996037037037</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4141</v>
+        <v>0.4775592592592592</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6260851851851852</v>
+        <v>0.6487518518518518</v>
       </c>
       <c r="E7" t="n">
-        <v>60.56</v>
+        <v>65.22</v>
       </c>
       <c r="F7" t="n">
         <v>49</v>
       </c>
       <c r="G7" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H7" t="n">
-        <v>65.84020404403337</v>
+        <v>82.3211057527236</v>
       </c>
       <c r="I7" t="n">
-        <v>-40.12259619527805</v>
+        <v>1.238152466155348</v>
       </c>
       <c r="J7" t="n">
-        <v>182.60892290789</v>
+        <v>150.5662047925986</v>
       </c>
     </row>
     <row r="8">
@@ -677,31 +677,31 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.5220019259259259</v>
+        <v>0.5675640740740741</v>
       </c>
       <c r="C8" t="n">
-        <v>0.432262962962963</v>
+        <v>0.3424851851851852</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6029148148148148</v>
+        <v>0.6433481481481481</v>
       </c>
       <c r="E8" t="n">
-        <v>61.78</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="H8" t="n">
-        <v>62.07404579719394</v>
+        <v>82.74750034350431</v>
       </c>
       <c r="I8" t="n">
-        <v>-42.45578179109486</v>
+        <v>6.472929132638622</v>
       </c>
       <c r="J8" t="n">
-        <v>175.2251724378326</v>
+        <v>165.064397023647</v>
       </c>
     </row>
     <row r="9">
@@ -709,31 +709,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.521454888888889</v>
+        <v>0.5643714814814814</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3044037037037037</v>
+        <v>0.4818407407407407</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6334888888888889</v>
+        <v>0.6400518518518519</v>
       </c>
       <c r="E9" t="n">
-        <v>60.78</v>
+        <v>65.2</v>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="G9" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H9" t="n">
-        <v>68.40916049372933</v>
+        <v>80.00390668729642</v>
       </c>
       <c r="I9" t="n">
-        <v>-9.345562075084953</v>
+        <v>-18.24926618211332</v>
       </c>
       <c r="J9" t="n">
-        <v>145.8477712548984</v>
+        <v>164.5562823917575</v>
       </c>
     </row>
     <row r="10">
@@ -741,31 +741,31 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5214288148148148</v>
+        <v>0.5643814814814815</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3478851851851852</v>
+        <v>0.4253407407407407</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6107037037037037</v>
+        <v>0.6343148148148148</v>
       </c>
       <c r="E10" t="n">
-        <v>61.68</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="G10" t="n">
         <v>79</v>
       </c>
       <c r="H10" t="n">
-        <v>60.63091283814693</v>
+        <v>82.82911259650494</v>
       </c>
       <c r="I10" t="n">
-        <v>-25.94193184332472</v>
+        <v>2.908661972643985</v>
       </c>
       <c r="J10" t="n">
-        <v>151.9621758472926</v>
+        <v>163.592534529219</v>
       </c>
     </row>
     <row r="11">
@@ -773,31 +773,31 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5302404074074074</v>
+        <v>0.5666867407407409</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3957148148148148</v>
+        <v>0.4561259259259259</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6469851851851852</v>
+        <v>0.644537037037037</v>
       </c>
       <c r="E11" t="n">
-        <v>62.4</v>
+        <v>65.38</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="G11" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H11" t="n">
-        <v>56.72790096507921</v>
+        <v>84.98901172891317</v>
       </c>
       <c r="I11" t="n">
-        <v>-31.7799349860044</v>
+        <v>10.53946227747928</v>
       </c>
       <c r="J11" t="n">
-        <v>192.8367112859787</v>
+        <v>176.4971695529352</v>
       </c>
     </row>
     <row r="12">
@@ -805,31 +805,31 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.5210279259259258</v>
+        <v>0.5620597407407407</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4184148148148148</v>
+        <v>0.4620481481481482</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6101962962962963</v>
+        <v>0.6354962962962963</v>
       </c>
       <c r="E12" t="n">
-        <v>61.39</v>
+        <v>65.53</v>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G12" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H12" t="n">
-        <v>62.28335019706451</v>
+        <v>87.14113004164643</v>
       </c>
       <c r="I12" t="n">
-        <v>-31.34354288016879</v>
+        <v>16.37300350792453</v>
       </c>
       <c r="J12" t="n">
-        <v>148.621185096678</v>
+        <v>179.5491304859773</v>
       </c>
     </row>
     <row r="13">
@@ -837,31 +837,31 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5250687407407407</v>
+        <v>0.5591932222222222</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4150481481481482</v>
+        <v>0.3986851851851852</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6166</v>
+        <v>0.661937037037037</v>
       </c>
       <c r="E13" t="n">
-        <v>61.67</v>
+        <v>64.94</v>
       </c>
       <c r="F13" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H13" t="n">
-        <v>66.41112040121038</v>
+        <v>85.98742853128749</v>
       </c>
       <c r="I13" t="n">
-        <v>-54.90255847412425</v>
+        <v>4.192215674820405</v>
       </c>
       <c r="J13" t="n">
-        <v>139.7073195915073</v>
+        <v>179.2791073715685</v>
       </c>
     </row>
     <row r="14">
@@ -869,31 +869,31 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.5181896666666667</v>
+        <v>0.5600286296296296</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3419592592592592</v>
+        <v>0.3885444444444445</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6141518518518518</v>
+        <v>0.6275851851851851</v>
       </c>
       <c r="E14" t="n">
-        <v>60.29</v>
+        <v>65.16</v>
       </c>
       <c r="F14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G14" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H14" t="n">
-        <v>65.3905431032839</v>
+        <v>84.85085576751973</v>
       </c>
       <c r="I14" t="n">
-        <v>-30.53435778254696</v>
+        <v>5.721506353208554</v>
       </c>
       <c r="J14" t="n">
-        <v>178.0886651413252</v>
+        <v>157.144015206877</v>
       </c>
     </row>
     <row r="15">
@@ -901,31 +901,31 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.522316962962963</v>
+        <v>0.5564100370370371</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3835629629629629</v>
+        <v>0.4266037037037037</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6046407407407407</v>
+        <v>0.6679592592592593</v>
       </c>
       <c r="E15" t="n">
-        <v>61.24</v>
+        <v>64.25</v>
       </c>
       <c r="F15" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G15" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H15" t="n">
-        <v>64.88582178605337</v>
+        <v>88.0751704519792</v>
       </c>
       <c r="I15" t="n">
-        <v>-16.366871958149</v>
+        <v>10.13954312328508</v>
       </c>
       <c r="J15" t="n">
-        <v>157.0469919313568</v>
+        <v>183.7118102543393</v>
       </c>
     </row>
     <row r="16">
@@ -933,31 +933,31 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.5280081481481482</v>
+        <v>0.5566993333333332</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3493592592592593</v>
+        <v>0.4060814814814815</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6180481481481481</v>
+        <v>0.6300592592592592</v>
       </c>
       <c r="E16" t="n">
-        <v>61.04</v>
+        <v>65.75</v>
       </c>
       <c r="F16" t="n">
         <v>44</v>
       </c>
       <c r="G16" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H16" t="n">
-        <v>75.84805138248103</v>
+        <v>81.28575551588746</v>
       </c>
       <c r="I16" t="n">
-        <v>-58.49262827201248</v>
+        <v>-1.533233418601441</v>
       </c>
       <c r="J16" t="n">
-        <v>186.1961043184861</v>
+        <v>195.3907902495494</v>
       </c>
     </row>
     <row r="17">
@@ -965,31 +965,31 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.5271155555555554</v>
+        <v>0.5547505185185185</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3208</v>
+        <v>0.4600037037037037</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6155555555555555</v>
+        <v>0.6320703703703704</v>
       </c>
       <c r="E17" t="n">
-        <v>60.33</v>
+        <v>65.11</v>
       </c>
       <c r="F17" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="G17" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H17" t="n">
-        <v>76.15568522905478</v>
+        <v>79.45047227998711</v>
       </c>
       <c r="I17" t="n">
-        <v>-9.610875802914848</v>
+        <v>4.668595298112425</v>
       </c>
       <c r="J17" t="n">
-        <v>170.7409765834084</v>
+        <v>144.7707954892744</v>
       </c>
     </row>
     <row r="18">
@@ -997,31 +997,31 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5219455555555556</v>
+        <v>0.5628175185185185</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4018962962962963</v>
+        <v>0.4673592592592593</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6116518518518519</v>
+        <v>0.6562592592592592</v>
       </c>
       <c r="E18" t="n">
-        <v>62.22</v>
+        <v>65.14</v>
       </c>
       <c r="F18" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G18" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H18" t="n">
-        <v>64.36133004351628</v>
+        <v>85.7544674863542</v>
       </c>
       <c r="I18" t="n">
-        <v>-28.60675650492305</v>
+        <v>-1.578296982085133</v>
       </c>
       <c r="J18" t="n">
-        <v>164.8144763972765</v>
+        <v>181.8938165565207</v>
       </c>
     </row>
     <row r="19">
@@ -1029,31 +1029,31 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.5206068518518518</v>
+        <v>0.5635297407407407</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3829888888888889</v>
+        <v>0.4645222222222222</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5987037037037037</v>
+        <v>0.6446888888888889</v>
       </c>
       <c r="E19" t="n">
-        <v>61.17</v>
+        <v>66.88</v>
       </c>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G19" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H19" t="n">
-        <v>72.97078806522045</v>
+        <v>76.65418216268004</v>
       </c>
       <c r="I19" t="n">
-        <v>-32.61649666185541</v>
+        <v>-13.72130608456643</v>
       </c>
       <c r="J19" t="n">
-        <v>177.0157540723133</v>
+        <v>171.389729288668</v>
       </c>
     </row>
     <row r="20">
@@ -1061,31 +1061,31 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.5246081481481482</v>
+        <v>0.5629181851851852</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3721962962962963</v>
+        <v>0.4663037037037037</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6352037037037037</v>
+        <v>0.6427185185185185</v>
       </c>
       <c r="E20" t="n">
-        <v>61.91</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G20" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H20" t="n">
-        <v>75.02673078376087</v>
+        <v>86.2470264925753</v>
       </c>
       <c r="I20" t="n">
-        <v>1.777356291392124</v>
+        <v>6.944800014536868</v>
       </c>
       <c r="J20" t="n">
-        <v>166.4765515132945</v>
+        <v>205.5599385571117</v>
       </c>
     </row>
     <row r="21">
@@ -1093,31 +1093,31 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.5214395555555555</v>
+        <v>0.5611974074074074</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4231925925925926</v>
+        <v>0.4763703703703704</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6052740740740741</v>
+        <v>0.6498444444444444</v>
       </c>
       <c r="E21" t="n">
-        <v>61.95</v>
+        <v>65.39</v>
       </c>
       <c r="F21" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G21" t="n">
         <v>80</v>
       </c>
       <c r="H21" t="n">
-        <v>67.15766078007282</v>
+        <v>81.19169397390402</v>
       </c>
       <c r="I21" t="n">
-        <v>-26.65464136175837</v>
+        <v>-15.70257413300316</v>
       </c>
       <c r="J21" t="n">
-        <v>155.8596842681941</v>
+        <v>178.5523473755369</v>
       </c>
     </row>
     <row r="22">
@@ -1125,31 +1125,31 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.5239178148148149</v>
+        <v>0.5679813703703703</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3939518518518518</v>
+        <v>0.4939703703703704</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6428888888888888</v>
+        <v>0.6518111111111111</v>
       </c>
       <c r="E22" t="n">
-        <v>62.49</v>
+        <v>65.06</v>
       </c>
       <c r="F22" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G22" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H22" t="n">
-        <v>77.91012233671766</v>
+        <v>84.1496019099071</v>
       </c>
       <c r="I22" t="n">
-        <v>-9.844433969445792</v>
+        <v>-13.26561560818657</v>
       </c>
       <c r="J22" t="n">
-        <v>154.0274809159025</v>
+        <v>177.4556714035666</v>
       </c>
     </row>
     <row r="23">
@@ -1157,31 +1157,31 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.530596111111111</v>
+        <v>0.5630438148148147</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4174148148148148</v>
+        <v>0.487962962962963</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6196481481481482</v>
+        <v>0.633762962962963</v>
       </c>
       <c r="E23" t="n">
-        <v>62.9</v>
+        <v>65.23</v>
       </c>
       <c r="F23" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G23" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H23" t="n">
-        <v>73.42958892682543</v>
+        <v>81.15441533533783</v>
       </c>
       <c r="I23" t="n">
-        <v>-32.922142829038</v>
+        <v>-15.19716325503611</v>
       </c>
       <c r="J23" t="n">
-        <v>149.4593549448675</v>
+        <v>172.5732243916112</v>
       </c>
     </row>
     <row r="24">
@@ -1189,31 +1189,31 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.5287630740740741</v>
+        <v>0.5664788148148149</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4506222222222222</v>
+        <v>0.4855111111111111</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6313296296296297</v>
+        <v>0.6417111111111111</v>
       </c>
       <c r="E24" t="n">
-        <v>62.2</v>
+        <v>67.05</v>
       </c>
       <c r="F24" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G24" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H24" t="n">
-        <v>68.26071168596214</v>
+        <v>85.45618993193389</v>
       </c>
       <c r="I24" t="n">
-        <v>-45.83750267237755</v>
+        <v>-9.256909627952535</v>
       </c>
       <c r="J24" t="n">
-        <v>171.8010570497254</v>
+        <v>191.8241052641861</v>
       </c>
     </row>
     <row r="25">
@@ -1221,31 +1221,31 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.5272600370370371</v>
+        <v>0.560862</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4206777777777778</v>
+        <v>0.4674592592592592</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6562629629629629</v>
+        <v>0.6372074074074074</v>
       </c>
       <c r="E25" t="n">
-        <v>61.46</v>
+        <v>64.94</v>
       </c>
       <c r="F25" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G25" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H25" t="n">
-        <v>78.06074140247266</v>
+        <v>79.29631594445043</v>
       </c>
       <c r="I25" t="n">
-        <v>-42.72284954713095</v>
+        <v>-8.805025839019027</v>
       </c>
       <c r="J25" t="n">
-        <v>159.2470220795887</v>
+        <v>164.6623350574675</v>
       </c>
     </row>
     <row r="26">
@@ -1253,31 +1253,31 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.5264131111111111</v>
+        <v>0.5572729999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4097296296296296</v>
+        <v>0.4532962962962963</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6178296296296296</v>
+        <v>0.6408296296296296</v>
       </c>
       <c r="E26" t="n">
-        <v>62.13</v>
+        <v>65.42</v>
       </c>
       <c r="F26" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G26" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H26" t="n">
-        <v>75.57277853641251</v>
+        <v>87.36311455453985</v>
       </c>
       <c r="I26" t="n">
-        <v>-23.36004286106032</v>
+        <v>7.381256340364127</v>
       </c>
       <c r="J26" t="n">
-        <v>169.9716681820073</v>
+        <v>204.2784560848912</v>
       </c>
     </row>
     <row r="27">
@@ -1285,31 +1285,31 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.5268755185185185</v>
+        <v>0.5705834814814815</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3598037037037037</v>
+        <v>0.4848074074074074</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6276111111111111</v>
+        <v>0.644974074074074</v>
       </c>
       <c r="E27" t="n">
-        <v>61.98</v>
+        <v>66.09</v>
       </c>
       <c r="F27" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G27" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H27" t="n">
-        <v>71.06832681717005</v>
+        <v>79.88522857649234</v>
       </c>
       <c r="I27" t="n">
-        <v>-26.08265097101236</v>
+        <v>-3.378178568235883</v>
       </c>
       <c r="J27" t="n">
-        <v>179.4440953469162</v>
+        <v>150.6322569806502</v>
       </c>
     </row>
     <row r="28">
@@ -1317,31 +1317,31 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.5229873703703704</v>
+        <v>0.5588641111111111</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4204185185185185</v>
+        <v>0.477637037037037</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5980037037037037</v>
+        <v>0.6229925925925925</v>
       </c>
       <c r="E28" t="n">
-        <v>60.92</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="G28" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H28" t="n">
-        <v>84.1513234324087</v>
+        <v>84.95019439696205</v>
       </c>
       <c r="I28" t="n">
-        <v>0.03882176356224498</v>
+        <v>-2.061407256159057</v>
       </c>
       <c r="J28" t="n">
-        <v>179.3311326559523</v>
+        <v>160.7113276587027</v>
       </c>
     </row>
     <row r="29">
@@ -1349,31 +1349,31 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.5250773703703705</v>
+        <v>0.5623604814814815</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3479444444444444</v>
+        <v>0.4888074074074074</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6037666666666667</v>
+        <v>0.6225185185185185</v>
       </c>
       <c r="E29" t="n">
-        <v>60.08</v>
+        <v>65.41</v>
       </c>
       <c r="F29" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="G29" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H29" t="n">
-        <v>80.08007160877894</v>
+        <v>88.43675188903531</v>
       </c>
       <c r="I29" t="n">
-        <v>-19.61093133028156</v>
+        <v>8.320669476399701</v>
       </c>
       <c r="J29" t="n">
-        <v>196.0124842222437</v>
+        <v>181.5416639184073</v>
       </c>
     </row>
     <row r="30">
@@ -1381,31 +1381,31 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.5243336666666667</v>
+        <v>0.572397888888889</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4253296296296296</v>
+        <v>0.4613074074074074</v>
       </c>
       <c r="D30" t="n">
-        <v>0.634974074074074</v>
+        <v>0.6485111111111111</v>
       </c>
       <c r="E30" t="n">
-        <v>61.81</v>
+        <v>66.42</v>
       </c>
       <c r="F30" t="n">
         <v>48</v>
       </c>
       <c r="G30" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H30" t="n">
-        <v>79.43377534579189</v>
+        <v>79.69790872366174</v>
       </c>
       <c r="I30" t="n">
-        <v>-3.043172424913736</v>
+        <v>-12.77123599608007</v>
       </c>
       <c r="J30" t="n">
-        <v>208.1965349075279</v>
+        <v>158.7397546121466</v>
       </c>
     </row>
     <row r="31">
@@ -1413,31 +1413,31 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.5310466666666668</v>
+        <v>0.5662183703703704</v>
       </c>
       <c r="C31" t="n">
-        <v>0.429762962962963</v>
+        <v>0.4692185185185185</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.6699259259259259</v>
       </c>
       <c r="E31" t="n">
-        <v>62.65</v>
+        <v>65.89</v>
       </c>
       <c r="F31" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G31" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H31" t="n">
-        <v>76.98066771223296</v>
+        <v>85.79432006132721</v>
       </c>
       <c r="I31" t="n">
-        <v>-19.77535904206761</v>
+        <v>-39.76697558127892</v>
       </c>
       <c r="J31" t="n">
-        <v>172.46776968957</v>
+        <v>171.9704091583479</v>
       </c>
     </row>
     <row r="32">
@@ -1445,31 +1445,31 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>0.5265191481481483</v>
+        <v>0.5617902962962963</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4288407407407407</v>
+        <v>0.4754037037037037</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5865</v>
+        <v>0.6581037037037037</v>
       </c>
       <c r="E32" t="n">
-        <v>61.49</v>
+        <v>64.94</v>
       </c>
       <c r="F32" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G32" t="n">
         <v>79</v>
       </c>
       <c r="H32" t="n">
-        <v>77.40089405294506</v>
+        <v>87.21403268050081</v>
       </c>
       <c r="I32" t="n">
-        <v>-11.97145221659526</v>
+        <v>-10.66993418462201</v>
       </c>
       <c r="J32" t="n">
-        <v>172.969052203813</v>
+        <v>183.4821705024138</v>
       </c>
     </row>
     <row r="33">
@@ -1477,31 +1477,31 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>0.5268329259259259</v>
+        <v>0.5613051111111111</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3524222222222222</v>
+        <v>0.4175222222222222</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6339814814814815</v>
+        <v>0.6467925925925926</v>
       </c>
       <c r="E33" t="n">
-        <v>62.15</v>
+        <v>64.28</v>
       </c>
       <c r="F33" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G33" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H33" t="n">
-        <v>81.37085086920385</v>
+        <v>85.68725722913403</v>
       </c>
       <c r="I33" t="n">
-        <v>-24.40823051660686</v>
+        <v>5.933612813419749</v>
       </c>
       <c r="J33" t="n">
-        <v>163.659075650219</v>
+        <v>168.0060911584178</v>
       </c>
     </row>
     <row r="34">
@@ -1509,31 +1509,31 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>0.5265042962962962</v>
+        <v>0.5647111851851853</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4185074074074074</v>
+        <v>0.4349962962962963</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6133481481481482</v>
+        <v>0.6298037037037038</v>
       </c>
       <c r="E34" t="n">
-        <v>62.56</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G34" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H34" t="n">
-        <v>77.05031225593557</v>
+        <v>81.96671707900622</v>
       </c>
       <c r="I34" t="n">
-        <v>-11.83920533705077</v>
+        <v>9.262808690013705</v>
       </c>
       <c r="J34" t="n">
-        <v>172.8202961283398</v>
+        <v>147.4127893763907</v>
       </c>
     </row>
     <row r="35">
@@ -1541,31 +1541,31 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>0.526524925925926</v>
+        <v>0.5648110740740742</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3855037037037037</v>
+        <v>0.3183592592592593</v>
       </c>
       <c r="D35" t="n">
-        <v>0.6170814814814815</v>
+        <v>0.6543111111111111</v>
       </c>
       <c r="E35" t="n">
-        <v>62.38</v>
+        <v>66.09</v>
       </c>
       <c r="F35" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G35" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H35" t="n">
-        <v>82.37237154029188</v>
+        <v>82.29903528067736</v>
       </c>
       <c r="I35" t="n">
-        <v>-15.72112797195226</v>
+        <v>-17.91066786478303</v>
       </c>
       <c r="J35" t="n">
-        <v>167.6294594811099</v>
+        <v>184.2253360814015</v>
       </c>
     </row>
     <row r="36">
@@ -1573,31 +1573,31 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>0.5394872592592592</v>
+        <v>0.5560593333333333</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3771962962962963</v>
+        <v>0.3788481481481482</v>
       </c>
       <c r="D36" t="n">
-        <v>0.6260851851851852</v>
+        <v>0.6570592592592592</v>
       </c>
       <c r="E36" t="n">
-        <v>63</v>
+        <v>64.8</v>
       </c>
       <c r="F36" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G36" t="n">
         <v>81</v>
       </c>
       <c r="H36" t="n">
-        <v>83.90768898050993</v>
+        <v>84.09832843789366</v>
       </c>
       <c r="I36" t="n">
-        <v>-28.77283945642551</v>
+        <v>-31.73354604304393</v>
       </c>
       <c r="J36" t="n">
-        <v>153.155640265775</v>
+        <v>183.9640802842406</v>
       </c>
     </row>
     <row r="37">
@@ -1605,31 +1605,31 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>0.5391845925925927</v>
+        <v>0.5583881851851852</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4407925925925926</v>
+        <v>0.3593740740740741</v>
       </c>
       <c r="D37" t="n">
-        <v>0.6215407407407407</v>
+        <v>0.6630148148148148</v>
       </c>
       <c r="E37" t="n">
-        <v>62.73</v>
+        <v>64.73</v>
       </c>
       <c r="F37" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G37" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H37" t="n">
-        <v>81.31242453518411</v>
+        <v>86.19809414696901</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.937669992683924</v>
+        <v>-27.20991354229486</v>
       </c>
       <c r="J37" t="n">
-        <v>210.3452069306026</v>
+        <v>160.5129910869836</v>
       </c>
     </row>
     <row r="38">
@@ -1637,31 +1637,31 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>0.5257113333333333</v>
+        <v>0.5651492592592593</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3370333333333334</v>
+        <v>0.4318407407407407</v>
       </c>
       <c r="D38" t="n">
-        <v>0.6203</v>
+        <v>0.6471370370370371</v>
       </c>
       <c r="E38" t="n">
-        <v>62</v>
+        <v>66.17</v>
       </c>
       <c r="F38" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G38" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H38" t="n">
-        <v>81.32592440041954</v>
+        <v>82.41974415506208</v>
       </c>
       <c r="I38" t="n">
-        <v>-5.701896730636604</v>
+        <v>-6.391832349978828</v>
       </c>
       <c r="J38" t="n">
-        <v>181.658973633656</v>
+        <v>161.6231606415348</v>
       </c>
     </row>
     <row r="39">
@@ -1669,31 +1669,31 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>0.5377163703703703</v>
+        <v>0.5644878148148148</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4082259259259259</v>
+        <v>0.4492777777777778</v>
       </c>
       <c r="D39" t="n">
-        <v>0.6286259259259259</v>
+        <v>0.6403333333333333</v>
       </c>
       <c r="E39" t="n">
-        <v>63.13</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G39" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H39" t="n">
-        <v>75.17212994018271</v>
+        <v>83.55579832800959</v>
       </c>
       <c r="I39" t="n">
-        <v>-24.8109636748974</v>
+        <v>14.96344867734716</v>
       </c>
       <c r="J39" t="n">
-        <v>146.3667248461803</v>
+        <v>165.1938434039837</v>
       </c>
     </row>
     <row r="40">
@@ -1701,31 +1701,31 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>0.5351008148148149</v>
+        <v>0.557022074074074</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2983740740740741</v>
+        <v>0.3678777777777778</v>
       </c>
       <c r="D40" t="n">
-        <v>0.6190629629629629</v>
+        <v>0.6339259259259259</v>
       </c>
       <c r="E40" t="n">
-        <v>62.07</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G40" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H40" t="n">
-        <v>81.87412105518419</v>
+        <v>85.75873118538202</v>
       </c>
       <c r="I40" t="n">
-        <v>-18.63868738480417</v>
+        <v>-9.794575422061781</v>
       </c>
       <c r="J40" t="n">
-        <v>184.6685073142047</v>
+        <v>164.6183838649362</v>
       </c>
     </row>
     <row r="41">
@@ -1733,31 +1733,31 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>0.5298341481481481</v>
+        <v>0.5630777037037037</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4114148148148148</v>
+        <v>0.3556222222222222</v>
       </c>
       <c r="D41" t="n">
-        <v>0.6246888888888888</v>
+        <v>0.6468481481481482</v>
       </c>
       <c r="E41" t="n">
-        <v>62.7</v>
+        <v>64.81</v>
       </c>
       <c r="F41" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="G41" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H41" t="n">
-        <v>82.83541452866776</v>
+        <v>83.33209010527997</v>
       </c>
       <c r="I41" t="n">
-        <v>-35.62610907324593</v>
+        <v>-6.351574055898471</v>
       </c>
       <c r="J41" t="n">
-        <v>173.2808068119244</v>
+        <v>156.8550622493757</v>
       </c>
     </row>
     <row r="42">
@@ -1765,31 +1765,31 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>0.5392297037037037</v>
+        <v>0.5533013333333334</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4131555555555556</v>
+        <v>0.4423666666666667</v>
       </c>
       <c r="D42" t="n">
-        <v>0.6469370370370371</v>
+        <v>0.6334037037037037</v>
       </c>
       <c r="E42" t="n">
-        <v>63.38</v>
+        <v>64.05</v>
       </c>
       <c r="F42" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G42" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H42" t="n">
-        <v>76.37213920536468</v>
+        <v>85.03507855244355</v>
       </c>
       <c r="I42" t="n">
-        <v>-23.70025294966574</v>
+        <v>-14.22042280497756</v>
       </c>
       <c r="J42" t="n">
-        <v>153.312150440279</v>
+        <v>184.913931214327</v>
       </c>
     </row>
     <row r="43">
@@ -1797,31 +1797,31 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>0.5350498518518519</v>
+        <v>0.5717539259259259</v>
       </c>
       <c r="C43" t="n">
-        <v>0.3563407407407407</v>
+        <v>0.4706407407407407</v>
       </c>
       <c r="D43" t="n">
-        <v>0.6117851851851852</v>
+        <v>0.6391518518518519</v>
       </c>
       <c r="E43" t="n">
-        <v>63.42</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G43" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H43" t="n">
-        <v>78.56868254871331</v>
+        <v>87.40444214500809</v>
       </c>
       <c r="I43" t="n">
-        <v>-38.46100494622851</v>
+        <v>-4.180072712201736</v>
       </c>
       <c r="J43" t="n">
-        <v>181.4772588700314</v>
+        <v>183.0905487136957</v>
       </c>
     </row>
     <row r="44">
@@ -1829,31 +1829,31 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>0.5404970370370371</v>
+        <v>0.5616401851851852</v>
       </c>
       <c r="C44" t="n">
-        <v>0.4479703703703704</v>
+        <v>0.3941111111111111</v>
       </c>
       <c r="D44" t="n">
-        <v>0.6347703703703703</v>
+        <v>0.6482259259259259</v>
       </c>
       <c r="E44" t="n">
-        <v>63.9</v>
+        <v>64.77</v>
       </c>
       <c r="F44" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G44" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H44" t="n">
-        <v>85.1693035223539</v>
+        <v>85.17886622842147</v>
       </c>
       <c r="I44" t="n">
-        <v>-39.75976607037143</v>
+        <v>9.775453618480064</v>
       </c>
       <c r="J44" t="n">
-        <v>181.3849197312995</v>
+        <v>188.7426388841208</v>
       </c>
     </row>
     <row r="45">
@@ -1861,31 +1861,31 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>0.5324664814814816</v>
+        <v>0.5630738888888888</v>
       </c>
       <c r="C45" t="n">
-        <v>0.3717740740740741</v>
+        <v>0.3356222222222222</v>
       </c>
       <c r="D45" t="n">
-        <v>0.6695518518518518</v>
+        <v>0.6241555555555556</v>
       </c>
       <c r="E45" t="n">
-        <v>63.84</v>
+        <v>65.11</v>
       </c>
       <c r="F45" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G45" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H45" t="n">
-        <v>81.62781151157722</v>
+        <v>85.51828682218353</v>
       </c>
       <c r="I45" t="n">
-        <v>-11.87955907111456</v>
+        <v>-10.4556263808174</v>
       </c>
       <c r="J45" t="n">
-        <v>174.8208871406707</v>
+        <v>159.4029929803927</v>
       </c>
     </row>
     <row r="46">
@@ -1893,31 +1893,31 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>0.5356944444444445</v>
+        <v>0.567391</v>
       </c>
       <c r="C46" t="n">
-        <v>0.3344925925925926</v>
+        <v>0.4406222222222222</v>
       </c>
       <c r="D46" t="n">
-        <v>0.6206148148148148</v>
+        <v>0.6370259259259259</v>
       </c>
       <c r="E46" t="n">
-        <v>63.49</v>
+        <v>66.06</v>
       </c>
       <c r="F46" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G46" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H46" t="n">
-        <v>83.58446452017888</v>
+        <v>88.55575114636777</v>
       </c>
       <c r="I46" t="n">
-        <v>-5.462059386587963</v>
+        <v>7.79259709787684</v>
       </c>
       <c r="J46" t="n">
-        <v>173.6110812957865</v>
+        <v>151.7944385215775</v>
       </c>
     </row>
     <row r="47">
@@ -1925,31 +1925,31 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>0.538398074074074</v>
+        <v>0.5701726296296296</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4188962962962963</v>
+        <v>0.4649925925925926</v>
       </c>
       <c r="D47" t="n">
-        <v>0.6283407407407408</v>
+        <v>0.6573296296296296</v>
       </c>
       <c r="E47" t="n">
-        <v>63.49</v>
+        <v>65.44</v>
       </c>
       <c r="F47" t="n">
         <v>44</v>
       </c>
       <c r="G47" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H47" t="n">
-        <v>84.68690075073965</v>
+        <v>86.94172808504626</v>
       </c>
       <c r="I47" t="n">
-        <v>-29.55348301947522</v>
+        <v>8.815464799302733</v>
       </c>
       <c r="J47" t="n">
-        <v>169.210774109203</v>
+        <v>152.4746491881633</v>
       </c>
     </row>
     <row r="48">
@@ -1957,31 +1957,31 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>0.5383586296296298</v>
+        <v>0.5667057777777778</v>
       </c>
       <c r="C48" t="n">
-        <v>0.4395814814814815</v>
+        <v>0.4771111111111111</v>
       </c>
       <c r="D48" t="n">
-        <v>0.6374222222222222</v>
+        <v>0.6502407407407408</v>
       </c>
       <c r="E48" t="n">
-        <v>63.04</v>
+        <v>66.73</v>
       </c>
       <c r="F48" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G48" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H48" t="n">
-        <v>83.74369018756951</v>
+        <v>91.09578941350415</v>
       </c>
       <c r="I48" t="n">
-        <v>-27.10079991986814</v>
+        <v>17.46549026353642</v>
       </c>
       <c r="J48" t="n">
-        <v>170.661612219318</v>
+        <v>178.9252235733042</v>
       </c>
     </row>
     <row r="49">
@@ -1989,31 +1989,31 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>0.5431904444444444</v>
+        <v>0.5681600740740741</v>
       </c>
       <c r="C49" t="n">
-        <v>0.4047851851851852</v>
+        <v>0.4777111111111111</v>
       </c>
       <c r="D49" t="n">
-        <v>0.6477259259259259</v>
+        <v>0.6548740740740741</v>
       </c>
       <c r="E49" t="n">
-        <v>64.06999999999999</v>
+        <v>65.28</v>
       </c>
       <c r="F49" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G49" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H49" t="n">
-        <v>78.4511030311685</v>
+        <v>89.15581321040111</v>
       </c>
       <c r="I49" t="n">
-        <v>-45.6685979702785</v>
+        <v>-16.56222255104004</v>
       </c>
       <c r="J49" t="n">
-        <v>180.2438343646216</v>
+        <v>173.3013999315438</v>
       </c>
     </row>
     <row r="50">
@@ -2021,31 +2021,31 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>0.5458184444444444</v>
+        <v>0.5659462592592593</v>
       </c>
       <c r="C50" t="n">
-        <v>0.3991518518518519</v>
+        <v>0.4877148148148148</v>
       </c>
       <c r="D50" t="n">
-        <v>0.6397888888888889</v>
+        <v>0.6278888888888889</v>
       </c>
       <c r="E50" t="n">
-        <v>63.3</v>
+        <v>65.89</v>
       </c>
       <c r="F50" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G50" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H50" t="n">
-        <v>83.62263950171381</v>
+        <v>84.63856225725685</v>
       </c>
       <c r="I50" t="n">
-        <v>1.172115187758862</v>
+        <v>-36.8996555790715</v>
       </c>
       <c r="J50" t="n">
-        <v>166.7379328424279</v>
+        <v>165.46001680564</v>
       </c>
     </row>
     <row r="51">
@@ -2053,31 +2053,31 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>0.5477147777777778</v>
+        <v>0.5640568888888891</v>
       </c>
       <c r="C51" t="n">
-        <v>0.3723037037037037</v>
+        <v>0.4573962962962963</v>
       </c>
       <c r="D51" t="n">
-        <v>0.6593555555555556</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>64.34999999999999</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G51" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H51" t="n">
-        <v>76.27158452758569</v>
+        <v>85.42887727710963</v>
       </c>
       <c r="I51" t="n">
-        <v>-28.99220628208933</v>
+        <v>-21.20102894053487</v>
       </c>
       <c r="J51" t="n">
-        <v>176.137631536033</v>
+        <v>162.7165350352347</v>
       </c>
     </row>
     <row r="52">
@@ -2085,31 +2085,31 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>0.5428492222222223</v>
+        <v>0.5650432592592591</v>
       </c>
       <c r="C52" t="n">
-        <v>0.441337037037037</v>
+        <v>0.3740074074074074</v>
       </c>
       <c r="D52" t="n">
-        <v>0.6355888888888889</v>
+        <v>0.6434222222222222</v>
       </c>
       <c r="E52" t="n">
-        <v>63.68</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="F52" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G52" t="n">
         <v>80</v>
       </c>
       <c r="H52" t="n">
-        <v>84.9053215416895</v>
+        <v>82.91708101809743</v>
       </c>
       <c r="I52" t="n">
-        <v>-17.58960259822541</v>
+        <v>1.744801071975917</v>
       </c>
       <c r="J52" t="n">
-        <v>182.1104056944015</v>
+        <v>172.3230795186912</v>
       </c>
     </row>
     <row r="53">
@@ -2117,31 +2117,31 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>0.5395864074074074</v>
+        <v>0.5698805185185185</v>
       </c>
       <c r="C53" t="n">
-        <v>0.4016592592592593</v>
+        <v>0.4821777777777778</v>
       </c>
       <c r="D53" t="n">
-        <v>0.625237037037037</v>
+        <v>0.6480814814814815</v>
       </c>
       <c r="E53" t="n">
-        <v>63.04</v>
+        <v>66.2</v>
       </c>
       <c r="F53" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G53" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H53" t="n">
-        <v>83.31695346281678</v>
+        <v>79.64691617357963</v>
       </c>
       <c r="I53" t="n">
-        <v>-29.42294991841587</v>
+        <v>-9.035751664639168</v>
       </c>
       <c r="J53" t="n">
-        <v>177.5455367729524</v>
+        <v>142.842768575755</v>
       </c>
     </row>
     <row r="54">
@@ -2149,31 +2149,31 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>0.5450048888888889</v>
+        <v>0.5677033703703703</v>
       </c>
       <c r="C54" t="n">
-        <v>0.3576296296296296</v>
+        <v>0.4940814814814815</v>
       </c>
       <c r="D54" t="n">
-        <v>0.6622370370370371</v>
+        <v>0.6443703703703704</v>
       </c>
       <c r="E54" t="n">
-        <v>64.06</v>
+        <v>67.2</v>
       </c>
       <c r="F54" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G54" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H54" t="n">
-        <v>85.66950387114349</v>
+        <v>83.41464510469352</v>
       </c>
       <c r="I54" t="n">
-        <v>-67.61902576825071</v>
+        <v>4.297630278460554</v>
       </c>
       <c r="J54" t="n">
-        <v>157.3552423148263</v>
+        <v>155.3449700341619</v>
       </c>
     </row>
     <row r="55">
@@ -2181,31 +2181,31 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>0.5491988518518518</v>
+        <v>0.5723868518518517</v>
       </c>
       <c r="C55" t="n">
-        <v>0.432162962962963</v>
+        <v>0.4637111111111111</v>
       </c>
       <c r="D55" t="n">
-        <v>0.6256074074074074</v>
+        <v>0.6449925925925926</v>
       </c>
       <c r="E55" t="n">
-        <v>63.74</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F55" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G55" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H55" t="n">
-        <v>91.24723627094085</v>
+        <v>85.58258639639425</v>
       </c>
       <c r="I55" t="n">
-        <v>-21.26219483437975</v>
+        <v>-27.57209297796427</v>
       </c>
       <c r="J55" t="n">
-        <v>167.0369685718617</v>
+        <v>168.7945737904701</v>
       </c>
     </row>
     <row r="56">
@@ -2213,31 +2213,31 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>0.5391192222222222</v>
+        <v>0.5720006666666666</v>
       </c>
       <c r="C56" t="n">
-        <v>0.3785296296296296</v>
+        <v>0.4855518518518518</v>
       </c>
       <c r="D56" t="n">
-        <v>0.6260666666666667</v>
+        <v>0.649737037037037</v>
       </c>
       <c r="E56" t="n">
-        <v>64.28</v>
+        <v>66.66</v>
       </c>
       <c r="F56" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="G56" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H56" t="n">
-        <v>79.23919933281893</v>
+        <v>85.214295521761</v>
       </c>
       <c r="I56" t="n">
-        <v>-9.617912066191364</v>
+        <v>-15.24264234718359</v>
       </c>
       <c r="J56" t="n">
-        <v>170.5255062944754</v>
+        <v>180.6489107241098</v>
       </c>
     </row>
     <row r="57">
@@ -2245,31 +2245,31 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>0.546011</v>
+        <v>0.5707287407407408</v>
       </c>
       <c r="C57" t="n">
-        <v>0.4438481481481482</v>
+        <v>0.4964666666666667</v>
       </c>
       <c r="D57" t="n">
-        <v>0.6235740740740741</v>
+        <v>0.6577814814814815</v>
       </c>
       <c r="E57" t="n">
-        <v>64.94</v>
+        <v>66.92</v>
       </c>
       <c r="F57" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G57" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H57" t="n">
-        <v>87.81375896491531</v>
+        <v>86.08121450442421</v>
       </c>
       <c r="I57" t="n">
-        <v>-7.963289547129412</v>
+        <v>-8.412359516167511</v>
       </c>
       <c r="J57" t="n">
-        <v>196.35441365937</v>
+        <v>179.1746392021885</v>
       </c>
     </row>
     <row r="58">
@@ -2277,31 +2277,31 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>0.5448480740740741</v>
+        <v>0.5692574814814815</v>
       </c>
       <c r="C58" t="n">
-        <v>0.3954074074074074</v>
+        <v>0.4199259259259259</v>
       </c>
       <c r="D58" t="n">
-        <v>0.6472259259259259</v>
+        <v>0.6505925925925926</v>
       </c>
       <c r="E58" t="n">
-        <v>63.07</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G58" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H58" t="n">
-        <v>86.89278192671848</v>
+        <v>83.58719074676168</v>
       </c>
       <c r="I58" t="n">
-        <v>-9.69881911653972</v>
+        <v>-4.622118123735626</v>
       </c>
       <c r="J58" t="n">
-        <v>160.8058248167057</v>
+        <v>178.9310054055004</v>
       </c>
     </row>
     <row r="59">
@@ -2309,31 +2309,31 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>0.5479911111111112</v>
+        <v>0.5705421851851852</v>
       </c>
       <c r="C59" t="n">
-        <v>0.4118185185185185</v>
+        <v>0.4571407407407407</v>
       </c>
       <c r="D59" t="n">
-        <v>0.6232740740740741</v>
+        <v>0.6481555555555556</v>
       </c>
       <c r="E59" t="n">
-        <v>65.12</v>
+        <v>66.64</v>
       </c>
       <c r="F59" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G59" t="n">
         <v>81</v>
       </c>
       <c r="H59" t="n">
-        <v>84.87324567064732</v>
+        <v>88.39792183294095</v>
       </c>
       <c r="I59" t="n">
-        <v>3.300026163201752</v>
+        <v>9.143598880381514</v>
       </c>
       <c r="J59" t="n">
-        <v>155.6014888362015</v>
+        <v>182.3019980600856</v>
       </c>
     </row>
     <row r="60">
@@ -2341,31 +2341,31 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>0.549309925925926</v>
+        <v>0.5716484814814815</v>
       </c>
       <c r="C60" t="n">
-        <v>0.4332888888888889</v>
+        <v>0.4492518518518518</v>
       </c>
       <c r="D60" t="n">
-        <v>0.6497592592592593</v>
+        <v>0.6281111111111111</v>
       </c>
       <c r="E60" t="n">
-        <v>64.34</v>
+        <v>66.52</v>
       </c>
       <c r="F60" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G60" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H60" t="n">
-        <v>86.96912045332593</v>
+        <v>89.87734136585615</v>
       </c>
       <c r="I60" t="n">
-        <v>10.94874877007009</v>
+        <v>-20.68388562917831</v>
       </c>
       <c r="J60" t="n">
-        <v>177.2368565207087</v>
+        <v>174.2355666385876</v>
       </c>
     </row>
     <row r="61">
@@ -2373,31 +2373,31 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>0.5457921481481481</v>
+        <v>0.5695892962962963</v>
       </c>
       <c r="C61" t="n">
-        <v>0.4269037037037037</v>
+        <v>0.4508259259259259</v>
       </c>
       <c r="D61" t="n">
-        <v>0.6315148148148149</v>
+        <v>0.6531444444444444</v>
       </c>
       <c r="E61" t="n">
-        <v>64.16</v>
+        <v>65.67</v>
       </c>
       <c r="F61" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G61" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H61" t="n">
-        <v>85.78537824263626</v>
+        <v>89.64744487465788</v>
       </c>
       <c r="I61" t="n">
-        <v>-2.16097957437106</v>
+        <v>12.14520441763199</v>
       </c>
       <c r="J61" t="n">
-        <v>160.2805550588725</v>
+        <v>161.0182498526198</v>
       </c>
     </row>
     <row r="62">
@@ -2405,31 +2405,31 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>0.5489901481481482</v>
+        <v>0.5728541481481482</v>
       </c>
       <c r="C62" t="n">
-        <v>0.3842518518518518</v>
+        <v>0.4640592592592593</v>
       </c>
       <c r="D62" t="n">
-        <v>0.6421629629629629</v>
+        <v>0.6510851851851852</v>
       </c>
       <c r="E62" t="n">
-        <v>64.81999999999999</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="F62" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G62" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H62" t="n">
-        <v>90.11798287037185</v>
+        <v>90.11177658724739</v>
       </c>
       <c r="I62" t="n">
-        <v>15.42468703527528</v>
+        <v>-18.5511002027092</v>
       </c>
       <c r="J62" t="n">
-        <v>192.9488371541589</v>
+        <v>147.9407306865006</v>
       </c>
     </row>
     <row r="63">
@@ -2437,31 +2437,31 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>0.5589879259259259</v>
+        <v>0.5703298518518518</v>
       </c>
       <c r="C63" t="n">
-        <v>0.3786481481481481</v>
+        <v>0.4443740740740741</v>
       </c>
       <c r="D63" t="n">
-        <v>0.6479703703703704</v>
+        <v>0.6616481481481481</v>
       </c>
       <c r="E63" t="n">
-        <v>66.06999999999999</v>
+        <v>65.48</v>
       </c>
       <c r="F63" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G63" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H63" t="n">
-        <v>79.00412740267147</v>
+        <v>84.9541638896882</v>
       </c>
       <c r="I63" t="n">
-        <v>-14.64463864123033</v>
+        <v>-8.401437854004119</v>
       </c>
       <c r="J63" t="n">
-        <v>174.8415346979612</v>
+        <v>148.9899054143219</v>
       </c>
     </row>
     <row r="64">
@@ -2469,31 +2469,31 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>0.5589407037037037</v>
+        <v>0.5725385185185184</v>
       </c>
       <c r="C64" t="n">
-        <v>0.3412333333333333</v>
+        <v>0.4590148148148148</v>
       </c>
       <c r="D64" t="n">
-        <v>0.6358777777777778</v>
+        <v>0.6422111111111111</v>
       </c>
       <c r="E64" t="n">
-        <v>66.20999999999999</v>
+        <v>66.48</v>
       </c>
       <c r="F64" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G64" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H64" t="n">
-        <v>85.79811911172308</v>
+        <v>92.15393420301885</v>
       </c>
       <c r="I64" t="n">
-        <v>-18.53075296657964</v>
+        <v>12.24999261278134</v>
       </c>
       <c r="J64" t="n">
-        <v>168.3515926032832</v>
+        <v>204.6449566058617</v>
       </c>
     </row>
     <row r="65">
@@ -2501,31 +2501,31 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>0.5512547407407409</v>
+        <v>0.5758132222222222</v>
       </c>
       <c r="C65" t="n">
-        <v>0.390462962962963</v>
+        <v>0.4972777777777778</v>
       </c>
       <c r="D65" t="n">
-        <v>0.649974074074074</v>
+        <v>0.6464111111111112</v>
       </c>
       <c r="E65" t="n">
-        <v>64.79000000000001</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="F65" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G65" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H65" t="n">
-        <v>86.57527633685777</v>
+        <v>85.69396455073539</v>
       </c>
       <c r="I65" t="n">
-        <v>-6.786918718580726</v>
+        <v>6.127884771974173</v>
       </c>
       <c r="J65" t="n">
-        <v>199.5552312277002</v>
+        <v>174.6519834714098</v>
       </c>
     </row>
     <row r="66">
@@ -2533,31 +2533,31 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>0.5573103333333334</v>
+        <v>0.5673277407407408</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4705666666666667</v>
+        <v>0.453737037037037</v>
       </c>
       <c r="D66" t="n">
-        <v>0.6558148148148149</v>
+        <v>0.6301111111111111</v>
       </c>
       <c r="E66" t="n">
-        <v>64.72</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G66" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H66" t="n">
-        <v>88.74766222404101</v>
+        <v>91.65993072611616</v>
       </c>
       <c r="I66" t="n">
-        <v>9.625519136632452</v>
+        <v>-1.312777878423135</v>
       </c>
       <c r="J66" t="n">
-        <v>163.4062660754567</v>
+        <v>177.7559456881742</v>
       </c>
     </row>
     <row r="67">
@@ -2565,31 +2565,31 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>0.5546588518518518</v>
+        <v>0.5686149999999999</v>
       </c>
       <c r="C67" t="n">
-        <v>0.4279296296296296</v>
+        <v>0.2416037037037037</v>
       </c>
       <c r="D67" t="n">
-        <v>0.6508407407407407</v>
+        <v>0.6678666666666667</v>
       </c>
       <c r="E67" t="n">
-        <v>65.08</v>
+        <v>66.63</v>
       </c>
       <c r="F67" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="G67" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H67" t="n">
-        <v>86.12166752887984</v>
+        <v>89.78037435309359</v>
       </c>
       <c r="I67" t="n">
-        <v>-17.35498161408953</v>
+        <v>-16.47028170340253</v>
       </c>
       <c r="J67" t="n">
-        <v>172.8186406471854</v>
+        <v>164.7581635681026</v>
       </c>
     </row>
     <row r="68">
@@ -2597,31 +2597,31 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>0.5540552592592592</v>
+        <v>0.5678902222222222</v>
       </c>
       <c r="C68" t="n">
-        <v>0.4141</v>
+        <v>0.4551037037037037</v>
       </c>
       <c r="D68" t="n">
-        <v>0.6464037037037037</v>
+        <v>0.6407555555555555</v>
       </c>
       <c r="E68" t="n">
-        <v>65.09999999999999</v>
+        <v>65.97</v>
       </c>
       <c r="F68" t="n">
         <v>48</v>
       </c>
       <c r="G68" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H68" t="n">
-        <v>88.60821217891447</v>
+        <v>86.62078801206539</v>
       </c>
       <c r="I68" t="n">
-        <v>8.568326476483252</v>
+        <v>-12.040108884862</v>
       </c>
       <c r="J68" t="n">
-        <v>180.5491859683475</v>
+        <v>167.8445799305132</v>
       </c>
     </row>
     <row r="69">
@@ -2629,31 +2629,31 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>0.5572838518518519</v>
+        <v>0.5722433703703703</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4469814814814815</v>
+        <v>0.4987555555555556</v>
       </c>
       <c r="D69" t="n">
-        <v>0.627362962962963</v>
+        <v>0.6521518518518519</v>
       </c>
       <c r="E69" t="n">
-        <v>65.45</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F69" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="G69" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H69" t="n">
-        <v>83.84493870611736</v>
+        <v>86.46879926777603</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8607904966458717</v>
+        <v>-9.087441934975491</v>
       </c>
       <c r="J69" t="n">
-        <v>159.3973559958733</v>
+        <v>151.206294075868</v>
       </c>
     </row>
     <row r="70">
@@ -2661,31 +2661,31 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>0.5589104814814815</v>
+        <v>0.5693954814814814</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4220925925925926</v>
+        <v>0.4730037037037037</v>
       </c>
       <c r="D70" t="n">
-        <v>0.6268074074074074</v>
+        <v>0.6378814814814815</v>
       </c>
       <c r="E70" t="n">
-        <v>65.93000000000001</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G70" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H70" t="n">
-        <v>89.52098605239384</v>
+        <v>87.40577228060224</v>
       </c>
       <c r="I70" t="n">
-        <v>-18.94598018491183</v>
+        <v>14.90306108832499</v>
       </c>
       <c r="J70" t="n">
-        <v>171.8479415965019</v>
+        <v>167.6947394668903</v>
       </c>
     </row>
     <row r="71">
@@ -2693,31 +2693,31 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>0.5604205925925926</v>
+        <v>0.5692475925925925</v>
       </c>
       <c r="C71" t="n">
-        <v>0.4856851851851852</v>
+        <v>0.4497111111111111</v>
       </c>
       <c r="D71" t="n">
-        <v>0.6344259259259259</v>
+        <v>0.644462962962963</v>
       </c>
       <c r="E71" t="n">
-        <v>65.68000000000001</v>
+        <v>66.83</v>
       </c>
       <c r="F71" t="n">
         <v>49</v>
       </c>
       <c r="G71" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H71" t="n">
-        <v>91.78516814765106</v>
+        <v>87.85371595922274</v>
       </c>
       <c r="I71" t="n">
-        <v>-11.19763784326475</v>
+        <v>6.727664162413072</v>
       </c>
       <c r="J71" t="n">
-        <v>168.8102113650134</v>
+        <v>170.1538758188554</v>
       </c>
     </row>
     <row r="72">
@@ -2725,31 +2725,31 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>0.5514658888888888</v>
+        <v>0.5712021851851852</v>
       </c>
       <c r="C72" t="n">
-        <v>0.3965185185185185</v>
+        <v>0.4343074074074074</v>
       </c>
       <c r="D72" t="n">
-        <v>0.6282925925925926</v>
+        <v>0.6365851851851851</v>
       </c>
       <c r="E72" t="n">
-        <v>64.44</v>
+        <v>66.48</v>
       </c>
       <c r="F72" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G72" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H72" t="n">
-        <v>89.88490371897623</v>
+        <v>83.08122212921626</v>
       </c>
       <c r="I72" t="n">
-        <v>-9.495958119147872</v>
+        <v>-37.60392989599894</v>
       </c>
       <c r="J72" t="n">
-        <v>164.8330358648563</v>
+        <v>156.9513852488097</v>
       </c>
     </row>
     <row r="73">
@@ -2757,31 +2757,31 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>0.5507258518518517</v>
+        <v>0.5770795185185185</v>
       </c>
       <c r="C73" t="n">
-        <v>0.3957740740740741</v>
+        <v>0.4940074074074074</v>
       </c>
       <c r="D73" t="n">
-        <v>0.6469370370370371</v>
+        <v>0.6396740740740741</v>
       </c>
       <c r="E73" t="n">
-        <v>63.19</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="F73" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G73" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H73" t="n">
-        <v>90.72333150300716</v>
+        <v>90.22239649622848</v>
       </c>
       <c r="I73" t="n">
-        <v>12.26119279233178</v>
+        <v>15.03127690700225</v>
       </c>
       <c r="J73" t="n">
-        <v>165.9178426379855</v>
+        <v>178.9377117418554</v>
       </c>
     </row>
     <row r="74">
@@ -2789,31 +2789,31 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>0.5614564074074074</v>
+        <v>0.5700811481481481</v>
       </c>
       <c r="C74" t="n">
-        <v>0.4565296296296296</v>
+        <v>0.4640444444444444</v>
       </c>
       <c r="D74" t="n">
-        <v>0.6516592592592593</v>
+        <v>0.6502148148148148</v>
       </c>
       <c r="E74" t="n">
-        <v>66.02</v>
+        <v>66.47</v>
       </c>
       <c r="F74" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G74" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H74" t="n">
-        <v>83.74575505882966</v>
+        <v>87.98219180988424</v>
       </c>
       <c r="I74" t="n">
-        <v>-6.361861596420667</v>
+        <v>2.55540191388242</v>
       </c>
       <c r="J74" t="n">
-        <v>172.0466665133164</v>
+        <v>178.0845038468741</v>
       </c>
     </row>
     <row r="75">
@@ -2821,31 +2821,31 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>0.5583991481481482</v>
+        <v>0.5669672962962964</v>
       </c>
       <c r="C75" t="n">
-        <v>0.3766296296296296</v>
+        <v>0.4260888888888889</v>
       </c>
       <c r="D75" t="n">
-        <v>0.6484074074074074</v>
+        <v>0.6482777777777777</v>
       </c>
       <c r="E75" t="n">
-        <v>64.52</v>
+        <v>65.59</v>
       </c>
       <c r="F75" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G75" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H75" t="n">
-        <v>100.4168238533808</v>
+        <v>84.5414594065636</v>
       </c>
       <c r="I75" t="n">
-        <v>6.726506909255244</v>
+        <v>-28.91302876793858</v>
       </c>
       <c r="J75" t="n">
-        <v>202.9973575076138</v>
+        <v>162.5110227457381</v>
       </c>
     </row>
     <row r="76">
@@ -2853,31 +2853,31 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>0.5600524444444446</v>
+        <v>0.5721392222222222</v>
       </c>
       <c r="C76" t="n">
-        <v>0.4140222222222222</v>
+        <v>0.4650481481481482</v>
       </c>
       <c r="D76" t="n">
-        <v>0.6523555555555556</v>
+        <v>0.6408666666666667</v>
       </c>
       <c r="E76" t="n">
-        <v>65.63</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="F76" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G76" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H76" t="n">
-        <v>96.31918931050467</v>
+        <v>85.30648136210817</v>
       </c>
       <c r="I76" t="n">
-        <v>9.503144049876614</v>
+        <v>5.938758960168389</v>
       </c>
       <c r="J76" t="n">
-        <v>177.2310895439326</v>
+        <v>169.4715128455746</v>
       </c>
     </row>
     <row r="77">
@@ -2885,31 +2885,31 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>0.5581682962962964</v>
+        <v>0.5718834074074074</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4384444444444445</v>
+        <v>0.4814185185185185</v>
       </c>
       <c r="D77" t="n">
-        <v>0.6583666666666667</v>
+        <v>0.634862962962963</v>
       </c>
       <c r="E77" t="n">
-        <v>65.5</v>
+        <v>66.94</v>
       </c>
       <c r="F77" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G77" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H77" t="n">
-        <v>89.83921139303988</v>
+        <v>90.65003644222632</v>
       </c>
       <c r="I77" t="n">
-        <v>-25.77447041875979</v>
+        <v>-6.594774295432154</v>
       </c>
       <c r="J77" t="n">
-        <v>186.9810068189217</v>
+        <v>195.9670373099673</v>
       </c>
     </row>
     <row r="78">
@@ -2917,31 +2917,31 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>0.5572661851851852</v>
+        <v>0.5735093333333333</v>
       </c>
       <c r="C78" t="n">
-        <v>0.3438518518518519</v>
+        <v>0.4859333333333333</v>
       </c>
       <c r="D78" t="n">
-        <v>0.6233851851851852</v>
+        <v>0.6442629629629629</v>
       </c>
       <c r="E78" t="n">
-        <v>64.59</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="F78" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="G78" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H78" t="n">
-        <v>91.62791162837708</v>
+        <v>83.19951458555624</v>
       </c>
       <c r="I78" t="n">
-        <v>10.29471872925952</v>
+        <v>2.553587126976373</v>
       </c>
       <c r="J78" t="n">
-        <v>204.0924455366645</v>
+        <v>166.4651701254081</v>
       </c>
     </row>
     <row r="79">
@@ -2949,16 +2949,16 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>0.5642662222222223</v>
+        <v>0.5776429629629629</v>
       </c>
       <c r="C79" t="n">
-        <v>0.3949888888888889</v>
+        <v>0.4852518518518519</v>
       </c>
       <c r="D79" t="n">
-        <v>0.640837037037037</v>
+        <v>0.6552</v>
       </c>
       <c r="E79" t="n">
-        <v>66.44</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="F79" t="n">
         <v>46</v>
@@ -2967,13 +2967,13 @@
         <v>82</v>
       </c>
       <c r="H79" t="n">
-        <v>94.01776371394033</v>
+        <v>89.53751276501862</v>
       </c>
       <c r="I79" t="n">
-        <v>18.20300933123309</v>
+        <v>-0.5097771562413307</v>
       </c>
       <c r="J79" t="n">
-        <v>176.0421933305749</v>
+        <v>155.1238341039763</v>
       </c>
     </row>
     <row r="80">
@@ -2981,31 +2981,31 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>0.5593542222222222</v>
+        <v>0.5674473333333334</v>
       </c>
       <c r="C80" t="n">
-        <v>0.4058740740740741</v>
+        <v>0.4539111111111111</v>
       </c>
       <c r="D80" t="n">
-        <v>0.6408</v>
+        <v>0.6341111111111111</v>
       </c>
       <c r="E80" t="n">
-        <v>65.73999999999999</v>
+        <v>64.87</v>
       </c>
       <c r="F80" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="G80" t="n">
         <v>84</v>
       </c>
       <c r="H80" t="n">
-        <v>91.33339014366304</v>
+        <v>91.46212699416675</v>
       </c>
       <c r="I80" t="n">
-        <v>20.71722282712735</v>
+        <v>-21.82973100281279</v>
       </c>
       <c r="J80" t="n">
-        <v>165.9956558901058</v>
+        <v>174.2057815973113</v>
       </c>
     </row>
     <row r="81">
@@ -3013,31 +3013,31 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>0.5641812962962963</v>
+        <v>0.5757845185185185</v>
       </c>
       <c r="C81" t="n">
-        <v>0.3165518518518519</v>
+        <v>0.4864222222222222</v>
       </c>
       <c r="D81" t="n">
-        <v>0.6372185185185185</v>
+        <v>0.6578555555555555</v>
       </c>
       <c r="E81" t="n">
-        <v>66.11</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="F81" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G81" t="n">
         <v>82</v>
       </c>
       <c r="H81" t="n">
-        <v>90.7529544936648</v>
+        <v>81.19853025928687</v>
       </c>
       <c r="I81" t="n">
-        <v>-35.23626162237944</v>
+        <v>-16.02283326195892</v>
       </c>
       <c r="J81" t="n">
-        <v>188.6344814759378</v>
+        <v>175.7636056101272</v>
       </c>
     </row>
     <row r="82">
@@ -3045,31 +3045,31 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>0.5603006296296297</v>
+        <v>0.5713600370370371</v>
       </c>
       <c r="C82" t="n">
-        <v>0.3935777777777778</v>
+        <v>0.4772</v>
       </c>
       <c r="D82" t="n">
-        <v>0.6490814814814815</v>
+        <v>0.6398925925925926</v>
       </c>
       <c r="E82" t="n">
-        <v>66.08</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="F82" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G82" t="n">
         <v>85</v>
       </c>
       <c r="H82" t="n">
-        <v>90.17335502152736</v>
+        <v>84.47741423225285</v>
       </c>
       <c r="I82" t="n">
-        <v>-30.41706812930979</v>
+        <v>-48.06876788023514</v>
       </c>
       <c r="J82" t="n">
-        <v>163.6373837716181</v>
+        <v>165.2916637946118</v>
       </c>
     </row>
     <row r="83">
@@ -3077,31 +3077,31 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>0.5656834444444444</v>
+        <v>0.579186888888889</v>
       </c>
       <c r="C83" t="n">
-        <v>0.4522777777777778</v>
+        <v>0.4314296296296296</v>
       </c>
       <c r="D83" t="n">
-        <v>0.6591777777777778</v>
+        <v>0.6381259259259259</v>
       </c>
       <c r="E83" t="n">
-        <v>66.29000000000001</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="F83" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G83" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H83" t="n">
-        <v>94.95142313228716</v>
+        <v>84.13191483780312</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.5773400895062561</v>
+        <v>2.00264903261975</v>
       </c>
       <c r="J83" t="n">
-        <v>199.2421595359959</v>
+        <v>174.1790285134812</v>
       </c>
     </row>
     <row r="84">
@@ -3109,31 +3109,31 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>0.563547851851852</v>
+        <v>0.5684506296296297</v>
       </c>
       <c r="C84" t="n">
-        <v>0.4725407407407408</v>
+        <v>0.4320888888888889</v>
       </c>
       <c r="D84" t="n">
-        <v>0.6472962962962963</v>
+        <v>0.6482814814814815</v>
       </c>
       <c r="E84" t="n">
-        <v>67.09</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="F84" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G84" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H84" t="n">
-        <v>85.79421458223622</v>
+        <v>87.75875436283825</v>
       </c>
       <c r="I84" t="n">
-        <v>1.409197891529615</v>
+        <v>-15.01941002992432</v>
       </c>
       <c r="J84" t="n">
-        <v>217.8265508176509</v>
+        <v>175.2914981834656</v>
       </c>
     </row>
     <row r="85">
@@ -3141,31 +3141,31 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>0.5629772222222222</v>
+        <v>0.5752501481481481</v>
       </c>
       <c r="C85" t="n">
-        <v>0.4447259259259259</v>
+        <v>0.4736740740740741</v>
       </c>
       <c r="D85" t="n">
-        <v>0.6612296296296296</v>
+        <v>0.6487814814814815</v>
       </c>
       <c r="E85" t="n">
-        <v>65.75</v>
+        <v>67.08</v>
       </c>
       <c r="F85" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G85" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H85" t="n">
-        <v>91.60726457270528</v>
+        <v>87.46738850415771</v>
       </c>
       <c r="I85" t="n">
-        <v>12.39892402503106</v>
+        <v>-9.735245234631474</v>
       </c>
       <c r="J85" t="n">
-        <v>174.9368335671558</v>
+        <v>192.2924686386569</v>
       </c>
     </row>
     <row r="86">
@@ -3173,31 +3173,31 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>0.5613406296296296</v>
+        <v>0.5756514814814815</v>
       </c>
       <c r="C86" t="n">
-        <v>0.4455481481481481</v>
+        <v>0.4742185185185185</v>
       </c>
       <c r="D86" t="n">
-        <v>0.6311148148148148</v>
+        <v>0.6472222222222223</v>
       </c>
       <c r="E86" t="n">
-        <v>65.59999999999999</v>
+        <v>67.36</v>
       </c>
       <c r="F86" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G86" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H86" t="n">
-        <v>92.39739305732947</v>
+        <v>86.56138306386261</v>
       </c>
       <c r="I86" t="n">
-        <v>3.806296733123794</v>
+        <v>-1.98006110771669</v>
       </c>
       <c r="J86" t="n">
-        <v>191.8292695688223</v>
+        <v>184.9759379936106</v>
       </c>
     </row>
     <row r="87">
@@ -3205,31 +3205,31 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>0.5705976666666667</v>
+        <v>0.5710586296296295</v>
       </c>
       <c r="C87" t="n">
-        <v>0.4757037037037037</v>
+        <v>0.4575259259259259</v>
       </c>
       <c r="D87" t="n">
-        <v>0.6438148148148148</v>
+        <v>0.6476666666666666</v>
       </c>
       <c r="E87" t="n">
-        <v>66.38</v>
+        <v>67.05</v>
       </c>
       <c r="F87" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G87" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H87" t="n">
-        <v>89.06326353562861</v>
+        <v>82.64278619303973</v>
       </c>
       <c r="I87" t="n">
-        <v>-45.77179434281317</v>
+        <v>-11.08169046316596</v>
       </c>
       <c r="J87" t="n">
-        <v>182.9045303495259</v>
+        <v>175.9417445153552</v>
       </c>
     </row>
     <row r="88">
@@ -3237,31 +3237,31 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>0.564973962962963</v>
+        <v>0.5689184074074075</v>
       </c>
       <c r="C88" t="n">
-        <v>0.4824555555555556</v>
+        <v>0.4817222222222222</v>
       </c>
       <c r="D88" t="n">
-        <v>0.6486851851851851</v>
+        <v>0.6266592592592592</v>
       </c>
       <c r="E88" t="n">
-        <v>65.84999999999999</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="F88" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G88" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H88" t="n">
-        <v>89.72178659692963</v>
+        <v>90.51828695281945</v>
       </c>
       <c r="I88" t="n">
-        <v>-29.27213165192148</v>
+        <v>19.8658626433045</v>
       </c>
       <c r="J88" t="n">
-        <v>172.6142546301243</v>
+        <v>212.3424161818236</v>
       </c>
     </row>
     <row r="89">
@@ -3269,31 +3269,31 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>0.5592331481481482</v>
+        <v>0.5739963333333334</v>
       </c>
       <c r="C89" t="n">
-        <v>0.3833074074074074</v>
+        <v>0.4787962962962963</v>
       </c>
       <c r="D89" t="n">
-        <v>0.6333185185185185</v>
+        <v>0.6384148148148148</v>
       </c>
       <c r="E89" t="n">
-        <v>65.15000000000001</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="F89" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="G89" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H89" t="n">
-        <v>96.00211724192559</v>
+        <v>84.62720282708823</v>
       </c>
       <c r="I89" t="n">
-        <v>7.737363975132983</v>
+        <v>-7.710446448472684</v>
       </c>
       <c r="J89" t="n">
-        <v>169.9818833466676</v>
+        <v>164.7471070328332</v>
       </c>
     </row>
     <row r="90">
@@ -3301,31 +3301,31 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>0.5632782222222222</v>
+        <v>0.5691002222222222</v>
       </c>
       <c r="C90" t="n">
-        <v>0.4765740740740741</v>
+        <v>0.4737</v>
       </c>
       <c r="D90" t="n">
-        <v>0.6643555555555556</v>
+        <v>0.6346407407407407</v>
       </c>
       <c r="E90" t="n">
-        <v>65.86</v>
+        <v>66.94</v>
       </c>
       <c r="F90" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G90" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H90" t="n">
-        <v>91.75931325453068</v>
+        <v>82.54977689894629</v>
       </c>
       <c r="I90" t="n">
-        <v>15.16980946591154</v>
+        <v>-40.47693281046389</v>
       </c>
       <c r="J90" t="n">
-        <v>167.0991429676382</v>
+        <v>164.0635549887341</v>
       </c>
     </row>
     <row r="91">
@@ -3333,31 +3333,31 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>0.5669944444444444</v>
+        <v>0.5800974074074073</v>
       </c>
       <c r="C91" t="n">
-        <v>0.4673259259259259</v>
+        <v>0.4661148148148148</v>
       </c>
       <c r="D91" t="n">
-        <v>0.6380740740740741</v>
+        <v>0.6593481481481481</v>
       </c>
       <c r="E91" t="n">
-        <v>66.53</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="F91" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="G91" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H91" t="n">
-        <v>86.94761663766629</v>
+        <v>89.95664364504572</v>
       </c>
       <c r="I91" t="n">
-        <v>-9.907657297519989</v>
+        <v>-23.85963334108476</v>
       </c>
       <c r="J91" t="n">
-        <v>195.2354882522366</v>
+        <v>160.3021192352184</v>
       </c>
     </row>
     <row r="92">
@@ -3365,31 +3365,31 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>0.5678976666666666</v>
+        <v>0.577219962962963</v>
       </c>
       <c r="C92" t="n">
-        <v>0.449237037037037</v>
+        <v>0.4525814814814815</v>
       </c>
       <c r="D92" t="n">
-        <v>0.6333222222222222</v>
+        <v>0.6495962962962963</v>
       </c>
       <c r="E92" t="n">
-        <v>66.31</v>
+        <v>66.97</v>
       </c>
       <c r="F92" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G92" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H92" t="n">
-        <v>91.74173042911885</v>
+        <v>80.31636993322081</v>
       </c>
       <c r="I92" t="n">
-        <v>0.8542450512533168</v>
+        <v>3.816887158839915</v>
       </c>
       <c r="J92" t="n">
-        <v>177.7801079386385</v>
+        <v>171.3269891007791</v>
       </c>
     </row>
     <row r="93">
@@ -3397,31 +3397,31 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>0.5644990740740741</v>
+        <v>0.5762262962962964</v>
       </c>
       <c r="C93" t="n">
-        <v>0.4792592592592593</v>
+        <v>0.4607518518518519</v>
       </c>
       <c r="D93" t="n">
-        <v>0.6626777777777778</v>
+        <v>0.661962962962963</v>
       </c>
       <c r="E93" t="n">
-        <v>65.51000000000001</v>
+        <v>67.36</v>
       </c>
       <c r="F93" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="G93" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H93" t="n">
-        <v>95.34180227833004</v>
+        <v>85.85586736570551</v>
       </c>
       <c r="I93" t="n">
-        <v>21.75473616207427</v>
+        <v>-7.501581225610835</v>
       </c>
       <c r="J93" t="n">
-        <v>184.0786500264267</v>
+        <v>163.3565667527366</v>
       </c>
     </row>
     <row r="94">
@@ -3429,31 +3429,31 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>0.5618595555555556</v>
+        <v>0.5722792592592593</v>
       </c>
       <c r="C94" t="n">
-        <v>0.4741740740740741</v>
+        <v>0.4680333333333334</v>
       </c>
       <c r="D94" t="n">
-        <v>0.6412962962962963</v>
+        <v>0.6417296296296296</v>
       </c>
       <c r="E94" t="n">
-        <v>66.76000000000001</v>
+        <v>65.31</v>
       </c>
       <c r="F94" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G94" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H94" t="n">
-        <v>90.56635189299966</v>
+        <v>86.60037038009239</v>
       </c>
       <c r="I94" t="n">
-        <v>-12.35396663691499</v>
+        <v>-15.35719346004725</v>
       </c>
       <c r="J94" t="n">
-        <v>174.1377378650236</v>
+        <v>164.5656566693034</v>
       </c>
     </row>
     <row r="95">
@@ -3461,31 +3461,31 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>0.5726125925925927</v>
+        <v>0.5716282962962963</v>
       </c>
       <c r="C95" t="n">
-        <v>0.4905407407407407</v>
+        <v>0.458262962962963</v>
       </c>
       <c r="D95" t="n">
-        <v>0.6423851851851852</v>
+        <v>0.6443111111111111</v>
       </c>
       <c r="E95" t="n">
-        <v>65.65000000000001</v>
+        <v>66.42</v>
       </c>
       <c r="F95" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G95" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H95" t="n">
-        <v>92.24956650557941</v>
+        <v>90.58571864682264</v>
       </c>
       <c r="I95" t="n">
-        <v>-44.64661572007617</v>
+        <v>15.74442087730973</v>
       </c>
       <c r="J95" t="n">
-        <v>166.9296918473322</v>
+        <v>161.1780297998899</v>
       </c>
     </row>
     <row r="96">
@@ -3493,31 +3493,31 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>0.5645409629629631</v>
+        <v>0.5741767407407407</v>
       </c>
       <c r="C96" t="n">
-        <v>0.4580037037037037</v>
+        <v>0.481737037037037</v>
       </c>
       <c r="D96" t="n">
-        <v>0.6479222222222222</v>
+        <v>0.6437592592592593</v>
       </c>
       <c r="E96" t="n">
-        <v>65.44</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="F96" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G96" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H96" t="n">
-        <v>88.72494972902685</v>
+        <v>87.75133786655327</v>
       </c>
       <c r="I96" t="n">
-        <v>-9.393560104019288</v>
+        <v>10.44748790611618</v>
       </c>
       <c r="J96" t="n">
-        <v>190.4674456513839</v>
+        <v>168.9258046877185</v>
       </c>
     </row>
     <row r="97">
@@ -3525,31 +3525,31 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>0.5697713703703704</v>
+        <v>0.5739168888888887</v>
       </c>
       <c r="C97" t="n">
-        <v>0.4831444444444444</v>
+        <v>0.4620740740740741</v>
       </c>
       <c r="D97" t="n">
-        <v>0.6475222222222222</v>
+        <v>0.6469370370370371</v>
       </c>
       <c r="E97" t="n">
-        <v>66.12</v>
+        <v>65.66</v>
       </c>
       <c r="F97" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G97" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H97" t="n">
-        <v>90.6180977257816</v>
+        <v>83.50189480587252</v>
       </c>
       <c r="I97" t="n">
-        <v>13.47486995771945</v>
+        <v>-57.14925532814382</v>
       </c>
       <c r="J97" t="n">
-        <v>182.3663791303091</v>
+        <v>164.614497558308</v>
       </c>
     </row>
     <row r="98">
@@ -3557,31 +3557,31 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>0.5621826666666666</v>
+        <v>0.5738647777777777</v>
       </c>
       <c r="C98" t="n">
-        <v>0.4169074074074074</v>
+        <v>0.4775777777777778</v>
       </c>
       <c r="D98" t="n">
-        <v>0.6416925925925926</v>
+        <v>0.6562222222222223</v>
       </c>
       <c r="E98" t="n">
-        <v>66.59999999999999</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="F98" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G98" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H98" t="n">
-        <v>92.04792786572926</v>
+        <v>88.56137393329668</v>
       </c>
       <c r="I98" t="n">
-        <v>20.68523112133815</v>
+        <v>-25.3912827843707</v>
       </c>
       <c r="J98" t="n">
-        <v>175.0300961829688</v>
+        <v>179.7484705003812</v>
       </c>
     </row>
     <row r="99">
@@ -3589,31 +3589,31 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>0.5720847777777778</v>
+        <v>0.5803566666666666</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4728444444444445</v>
+        <v>0.4823962962962963</v>
       </c>
       <c r="D99" t="n">
-        <v>0.6521481481481481</v>
+        <v>0.6569777777777778</v>
       </c>
       <c r="E99" t="n">
-        <v>66.78</v>
+        <v>67.22</v>
       </c>
       <c r="F99" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G99" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H99" t="n">
-        <v>88.44745341051539</v>
+        <v>86.782744249308</v>
       </c>
       <c r="I99" t="n">
-        <v>2.921762163625065</v>
+        <v>-23.89674160842318</v>
       </c>
       <c r="J99" t="n">
-        <v>170.5345417471616</v>
+        <v>182.9641618658264</v>
       </c>
     </row>
     <row r="100">
@@ -3621,31 +3621,31 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>0.5630951111111111</v>
+        <v>0.5738538518518519</v>
       </c>
       <c r="C100" t="n">
-        <v>0.431562962962963</v>
+        <v>0.4226925925925926</v>
       </c>
       <c r="D100" t="n">
-        <v>0.6349333333333333</v>
+        <v>0.6473777777777778</v>
       </c>
       <c r="E100" t="n">
-        <v>65.87</v>
+        <v>66.34</v>
       </c>
       <c r="F100" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G100" t="n">
         <v>81</v>
       </c>
       <c r="H100" t="n">
-        <v>95.91463007231836</v>
+        <v>85.4132512890061</v>
       </c>
       <c r="I100" t="n">
-        <v>14.88881261432476</v>
+        <v>-12.79719053637537</v>
       </c>
       <c r="J100" t="n">
-        <v>175.5896872418979</v>
+        <v>184.9379836393478</v>
       </c>
     </row>
   </sheetData>
